--- a/setimo/FALTACURSAR_2312664_CCP_BACHAREL EM CIENCIA DA COMPUTACAO_18032026.xlsx
+++ b/setimo/FALTACURSAR_2312664_CCP_BACHAREL EM CIENCIA DA COMPUTACAO_18032026.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="62">
   <si>
     <t xml:space="preserve">SAU – SISTEMA ACADÊMICO UNIVERSITÁRIO
 CIÊNCIA DA COMPUTAÇÃO - BAC CIÊNCIA DA COMPUTAÇÃO - SEM ESPECIFICAÇÃO - 0/2023
@@ -29,9 +29,6 @@
 Data de geração: 18/03/2026 12:02h</t>
   </si>
   <si>
-    <t xml:space="preserve">Eletiva orientação</t>
-  </si>
-  <si>
     <t xml:space="preserve">Período</t>
   </si>
   <si>
@@ -197,7 +194,16 @@
     <t xml:space="preserve">ELO0900</t>
   </si>
   <si>
-    <t xml:space="preserve">ELETIVAS DE ORIENTACAO</t>
+    <t xml:space="preserve">ELETIVAS DE ORIENTACAO 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELETIVAS DE ORIENTACAO 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELETIVAS DE ORIENTACAO 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELETIVAS DE ORIENTACAO 4</t>
   </si>
   <si>
     <t xml:space="preserve">EXT0100</t>
@@ -218,6 +224,7 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -240,12 +247,14 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -308,41 +317,53 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -532,455 +553,547 @@
   <dimension ref="A1:I1048576"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="I1" s="0" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B3" s="6" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B4" s="6" t="s">
+      <c r="D4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <f aca="false">SUM(E3:E32)</f>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="B17" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="n">
+      <c r="C17" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E24" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="5" t="s">
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="E8" s="5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E22" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="n">
+      <c r="B25" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8"/>
+      <c r="B26" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8"/>
+      <c r="B27" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6"/>
+      <c r="B28" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E23" s="7" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="n">
+      <c r="B29" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E24" s="7" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="n">
+      <c r="B30" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E25" s="7" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="n">
+      <c r="B31" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E26" s="7" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="B32" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
